--- a/dados/excel/secretaria_map.xlsx
+++ b/dados/excel/secretaria_map.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
